--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1229-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1229-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{487F4AF1-AF6C-49B1-A8D5-1FE1A549EA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB0E9D3-660E-4AAD-8CD6-5458B351DB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{3C698DBB-1CB3-462F-ADB0-C69D2A078EAE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{61825A60-890A-4F45-9788-334623D78C10}"/>
   </bookViews>
   <sheets>
     <sheet name="1229-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1574,25 +1574,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B493F4B1-9CE0-4A54-B17F-803023C78644}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{421F6C97-35A6-4A43-9DF5-35BA5A73377F}">
   <dimension ref="A1:R71"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.77734375" customWidth="1"/>
-    <col min="8" max="9" width="7.44140625" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.375" customWidth="1"/>
+    <col min="6" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="9" width="9.375" customWidth="1"/>
+    <col min="10" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.375" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.375" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="Q1" s="35"/>
       <c r="R1" s="27"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
@@ -1650,7 +1650,7 @@
       <c r="Q2" s="37"/>
       <c r="R2" s="38"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>2</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="30"/>
       <c r="B4" s="31"/>
       <c r="C4" s="7"/>
@@ -1746,7 +1746,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="42">
         <v>2026</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="44">
         <v>2025</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="42">
         <v>2024</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="44">
         <v>2023</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>25</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="42">
         <v>2022</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>25</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="47"/>
       <c r="B27" s="22" t="s">
         <v>45</v>
@@ -2990,7 +2990,7 @@
       <c r="Q27" s="51"/>
       <c r="R27" s="51"/>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="44">
         <v>2021</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>25</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>25</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="56" t="s">
         <v>25</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="57"/>
       <c r="B33" s="24" t="s">
         <v>50</v>
@@ -3290,7 +3290,7 @@
       <c r="Q33" s="61"/>
       <c r="R33" s="61"/>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="42">
         <v>2020</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="44">
         <v>2019</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="42">
         <v>2018</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="44">
         <v>2017</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="42">
         <v>2016</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="44">
         <v>2015</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="42">
         <v>2014</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="44">
         <v>2013</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>5.0199999999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="42">
         <v>2012</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="44">
         <v>2011</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="42">
         <v>2010</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="44">
         <v>2009</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="42">
         <v>2008</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="44">
         <v>2007</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="42">
         <v>2006</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="44">
         <v>2005</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="42">
         <v>2004</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="44">
         <v>2003</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="42">
         <v>2002</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="44">
         <v>2001</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="42">
         <v>2000</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="44">
         <v>1999</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="42">
         <v>1998</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="44">
         <v>1997</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="42">
         <v>1996</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="44">
         <v>1995</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="42">
         <v>1994</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="44">
         <v>1993</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="42">
         <v>1992</v>
       </c>
@@ -4856,7 +4856,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="44">
         <v>1991</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="42">
         <v>1990</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="44">
         <v>1989</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="42">
         <v>1988</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="44">
         <v>1987</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="42">
         <v>1986</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="44">
         <v>1985</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="42">
         <v>1984</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="44" t="s">
         <v>51</v>
       </c>
